--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_apoyopot_a_2024_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_apoyopot_a_2024_coquimbo.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 15:05</t>
+    <t xml:space="preserve">2026-09-24 01:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1004,13 +1004,13 @@
         <v>15</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.43</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="22">
@@ -1027,13 +1027,13 @@
         <v>15</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-0.74</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="23">
@@ -1053,7 +1053,7 @@
         <v>-0.01</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0.54</v>
